--- a/site/leagues/proliga/2026_2027/xlsx/team_packs/team_pack_GAL.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/team_packs/team_pack_GAL.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D8" t="n">
